--- a/artfynd/A 40268-2021 artfynd.xlsx
+++ b/artfynd/A 40268-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40268-2021 artfynd.xlsx
+++ b/artfynd/A 40268-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74622196</v>
       </c>
       <c r="B2" t="n">
-        <v>95710</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475296.344882845</v>
+        <v>475296</v>
       </c>
       <c r="R2" t="n">
-        <v>6401540.277289972</v>
+        <v>6401540</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1988-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1988-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 40268-2021 artfynd.xlsx
+++ b/artfynd/A 40268-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74622196</v>
       </c>
       <c r="B2" t="n">
-        <v>97660</v>
+        <v>97661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40268-2021 artfynd.xlsx
+++ b/artfynd/A 40268-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74622196</v>
       </c>
       <c r="B2" t="n">
-        <v>97661</v>
+        <v>97688</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40268-2021 artfynd.xlsx
+++ b/artfynd/A 40268-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74622196</v>
       </c>
       <c r="B2" t="n">
-        <v>97688</v>
+        <v>97694</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40268-2021 artfynd.xlsx
+++ b/artfynd/A 40268-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74622196</v>
       </c>
       <c r="B2" t="n">
-        <v>97694</v>
+        <v>97701</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40268-2021 artfynd.xlsx
+++ b/artfynd/A 40268-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74622196</v>
       </c>
       <c r="B2" t="n">
-        <v>97701</v>
+        <v>97705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40268-2021 artfynd.xlsx
+++ b/artfynd/A 40268-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74622196</v>
       </c>
       <c r="B2" t="n">
-        <v>97705</v>
+        <v>97712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40268-2021 artfynd.xlsx
+++ b/artfynd/A 40268-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74622196</v>
       </c>
       <c r="B2" t="n">
-        <v>97715</v>
+        <v>97720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40268-2021 artfynd.xlsx
+++ b/artfynd/A 40268-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74622196</v>
       </c>
       <c r="B2" t="n">
-        <v>97720</v>
+        <v>97728</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40268-2021 artfynd.xlsx
+++ b/artfynd/A 40268-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74622196</v>
       </c>
       <c r="B2" t="n">
-        <v>97728</v>
+        <v>97738</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40268-2021 artfynd.xlsx
+++ b/artfynd/A 40268-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74622196</v>
+        <v>74119544</v>
       </c>
       <c r="B2" t="n">
-        <v>97738</v>
+        <v>101896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220250</v>
+        <v>220075</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7E0f 4023. SOM: Matteuccia struthiopteris. LEG: Roland Carlsson</t>
+          <t>Smålands flora 2007: KOO: 7E0f 4023. SOM: Chrysosplenium alternifolium. LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,6 +779,117 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>74622196</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>N om Frövik, Dalskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>475296</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6401540</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Järsnäs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1988-01-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1988-12-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 7E0f 4023. SOM: Matteuccia struthiopteris. LEG: Roland Carlsson</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Bäck, alkärr</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>

--- a/artfynd/A 40268-2021 artfynd.xlsx
+++ b/artfynd/A 40268-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74119544</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,8 +904,17 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74622196</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>